--- a/artfynd/A 49073-2020 artfynd.xlsx
+++ b/artfynd/A 49073-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820532</v>
+        <v>119820534</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487966</v>
+        <v>488133</v>
       </c>
       <c r="R2" t="n">
-        <v>6838096</v>
+        <v>6837907</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820534</v>
+        <v>119820533</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488133</v>
+        <v>487977</v>
       </c>
       <c r="R3" t="n">
-        <v>6837907</v>
+        <v>6837975</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820533</v>
+        <v>119820532</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487977</v>
+        <v>487966</v>
       </c>
       <c r="R4" t="n">
-        <v>6837975</v>
+        <v>6838096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 49073-2020 artfynd.xlsx
+++ b/artfynd/A 49073-2020 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820533</v>
+        <v>119820532</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487977</v>
+        <v>487966</v>
       </c>
       <c r="R3" t="n">
-        <v>6837975</v>
+        <v>6838096</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820532</v>
+        <v>119820533</v>
       </c>
       <c r="B4" t="n">
-        <v>97824</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487966</v>
+        <v>487977</v>
       </c>
       <c r="R4" t="n">
-        <v>6838096</v>
+        <v>6837975</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 49073-2020 artfynd.xlsx
+++ b/artfynd/A 49073-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820534</v>
+        <v>119820533</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488133</v>
+        <v>487977</v>
       </c>
       <c r="R2" t="n">
-        <v>6837907</v>
+        <v>6837975</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>119820532</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820533</v>
+        <v>119820534</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487977</v>
+        <v>488133</v>
       </c>
       <c r="R4" t="n">
-        <v>6837975</v>
+        <v>6837907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 49073-2020 artfynd.xlsx
+++ b/artfynd/A 49073-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820533</v>
+        <v>119820532</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>97847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487977</v>
+        <v>487966</v>
       </c>
       <c r="R2" t="n">
-        <v>6837975</v>
+        <v>6838096</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820532</v>
+        <v>119820534</v>
       </c>
       <c r="B3" t="n">
-        <v>97847</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487966</v>
+        <v>488133</v>
       </c>
       <c r="R3" t="n">
-        <v>6838096</v>
+        <v>6837907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820534</v>
+        <v>119820533</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488133</v>
+        <v>487977</v>
       </c>
       <c r="R4" t="n">
-        <v>6837907</v>
+        <v>6837975</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 49073-2020 artfynd.xlsx
+++ b/artfynd/A 49073-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820532</v>
+        <v>119820534</v>
       </c>
       <c r="B2" t="n">
-        <v>97847</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487966</v>
+        <v>488133</v>
       </c>
       <c r="R2" t="n">
-        <v>6838096</v>
+        <v>6837907</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820534</v>
+        <v>119820533</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488133</v>
+        <v>487977</v>
       </c>
       <c r="R3" t="n">
-        <v>6837907</v>
+        <v>6837975</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820533</v>
+        <v>119820532</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>97847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487977</v>
+        <v>487966</v>
       </c>
       <c r="R4" t="n">
-        <v>6837975</v>
+        <v>6838096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
